--- a/backend/data/uploads/MES/2026-07-06_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-06_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B78A080-7690-4DCB-AA3D-473C3D767B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E2784F5-6E24-401D-A113-F968D2888C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{295CA086-D157-4165-868E-FB86BB242BA2}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{80548089-001B-4367-BF7B-A5A79965CA4D}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C252D65E-1561-4E4D-A5D6-105759172E62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AF00DB-76BD-454C-9F2C-B57F35F9A323}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-06_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-06_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E2784F5-6E24-401D-A113-F968D2888C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64D3B7BB-A603-4B18-A4B7-BBDEAFA26CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{80548089-001B-4367-BF7B-A5A79965CA4D}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{7D2BD568-E673-4023-81A5-BBBFD9147C8B}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AF00DB-76BD-454C-9F2C-B57F35F9A323}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D637A4-61F7-4D9A-A678-4C355E777A04}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-06_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-06_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64D3B7BB-A603-4B18-A4B7-BBDEAFA26CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{515046A1-C03E-4817-99C5-A1E4C3998F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{7D2BD568-E673-4023-81A5-BBBFD9147C8B}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{9E4A3E4E-04B6-478F-A3D9-A03BACED9BE3}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D637A4-61F7-4D9A-A678-4C355E777A04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7EE202D-E05E-4640-A8EB-D2BE1E3C32DF}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
